--- a/Tracking.xlsx
+++ b/Tracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c.campbell\source\LearningResourcesRepo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56742015-AF17-4A66-BEBB-83B050C93D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05CE6326-07A0-4FF7-AC00-98F4AA2ADB13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="37">
   <si>
     <t>Week Start</t>
   </si>
@@ -98,10 +98,6 @@
     <t>144.8**</t>
   </si>
   <si>
-    <t>*Sunday and Monday munchie binge. Started back at gym on Tuesday
-**Dehydration weight lol</t>
-  </si>
-  <si>
     <t>17th march</t>
   </si>
   <si>
@@ -151,6 +147,12 @@
   </si>
   <si>
     <t>7th july</t>
+  </si>
+  <si>
+    <t>*Sunday and Monday munchie binge. Started back at gym on Tuesday</t>
+  </si>
+  <si>
+    <t>**Dehydration weight lol</t>
   </si>
 </sst>
 </file>
@@ -184,7 +186,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -206,6 +208,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -251,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -283,7 +291,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -302,21 +309,15 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -721,62 +722,60 @@
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="11">
         <v>149.80000000000001</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="11">
         <v>148.80000000000001</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="11">
         <v>147</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="11">
         <v>148</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="H7" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="J7" s="11" t="s">
-        <v>18</v>
-      </c>
+      <c r="J7" s="20"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="11">
         <v>147</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="11">
         <v>146.80000000000001</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="11">
         <v>145.80000000000001</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="11">
         <v>146.80000000000001</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="11">
         <v>145.6</v>
       </c>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
-      <c r="F9" s="13">
+      <c r="F9" s="12">
         <v>144.1</v>
       </c>
       <c r="G9" s="1"/>
@@ -784,13 +783,13 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
-      <c r="F10" s="13">
+      <c r="F10" s="12">
         <v>142.9</v>
       </c>
       <c r="G10" s="1"/>
@@ -798,27 +797,27 @@
     </row>
     <row r="11" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
-      <c r="F11" s="15">
+      <c r="F11" s="14">
         <v>141.4</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="14" t="s">
-        <v>22</v>
+      <c r="A12" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
-      <c r="F12" s="16">
+      <c r="F12" s="15">
         <v>139.9</v>
       </c>
       <c r="G12" s="1"/>
@@ -826,13 +825,13 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="13">
+      <c r="F13" s="12">
         <v>138.4</v>
       </c>
       <c r="G13" s="1"/>
@@ -840,121 +839,121 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="12">
+        <v>136.9</v>
+      </c>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+    </row>
+    <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="19">
-        <v>136.9</v>
-      </c>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-    </row>
-    <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="20" t="s">
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="14">
+        <v>135.4</v>
+      </c>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="15">
-        <v>135.4</v>
-      </c>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="13">
+      <c r="F16" s="12">
         <v>133.9</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F17" s="13">
+        <v>26</v>
+      </c>
+      <c r="F17" s="12">
         <v>132.4</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="15">
+        <v>130.9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F18" s="16">
-        <v>130.9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="23" t="s">
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="14">
+        <v>129.4</v>
+      </c>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="15">
-        <v>129.4</v>
-      </c>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="14" t="s">
+      <c r="F20" s="12">
+        <v>127.9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F20" s="13">
-        <v>127.9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="14" t="s">
+      <c r="F21" s="12">
+        <v>126.4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F21" s="13">
-        <v>126.4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="22" t="s">
+      <c r="F22" s="12">
+        <v>124.9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F22" s="13">
-        <v>124.9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="22" t="s">
+      <c r="F23" s="12">
+        <v>123.4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="13">
-        <v>123.4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="23" t="s">
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="14">
+        <v>121.9</v>
+      </c>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="21"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="15">
-        <v>121.9</v>
-      </c>
-      <c r="G24" s="21"/>
-      <c r="H24" s="21"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="F25" s="17">
+      <c r="F25" s="16">
         <v>120.4</v>
       </c>
     </row>
@@ -966,7 +965,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{056E0CB8-3717-44B6-8C25-482A108BBA5F}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.88671875" customWidth="1"/>
@@ -979,7 +978,7 @@
     <col min="8" max="8" width="34.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1005,7 +1004,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -1025,91 +1024,103 @@
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="11">
         <v>149.80000000000001</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="11">
         <v>148.80000000000001</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="11">
         <v>147</v>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="11">
         <v>148</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="11" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="11">
         <v>147</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="11">
         <v>146.80000000000001</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="11">
         <v>145.80000000000001</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="11">
         <v>146.80000000000001</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="11">
         <v>145.6</v>
       </c>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G4" s="11">
+        <v>144.4</v>
+      </c>
+      <c r="H4" s="11">
+        <v>144.6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="B5" s="19"/>
+      <c r="C5" s="1">
+        <v>145.4</v>
+      </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="13">
+      <c r="F5" s="12">
         <v>144.1</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="13">
+      <c r="F6" s="12">
         <v>142.9</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
-      <c r="F7" s="15">
+      <c r="F7" s="14">
         <v>141.4</v>
       </c>
       <c r="G7" s="4"/>
@@ -1161,14 +1172,14 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
-        <v>22</v>
+      <c r="A2" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="16">
+      <c r="F2" s="15">
         <v>139.9</v>
       </c>
       <c r="G2" s="1"/>
@@ -1176,13 +1187,13 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="13">
+      <c r="F3" s="12">
         <v>138.4</v>
       </c>
       <c r="G3" s="1"/>
@@ -1190,31 +1201,31 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="12">
+        <v>136.9</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="19">
-        <v>136.9</v>
-      </c>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-    </row>
-    <row r="5" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="15">
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="14">
         <v>135.4</v>
       </c>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1253,42 +1264,42 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="13">
+      <c r="A2" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="12">
         <v>133.9</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="13">
+        <v>26</v>
+      </c>
+      <c r="F3" s="12">
         <v>132.4</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="15">
+        <v>130.9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="16">
-        <v>130.9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="15">
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="14">
         <v>129.4</v>
       </c>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1327,50 +1338,50 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="12">
+        <v>127.9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="13">
-        <v>127.9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="s">
+      <c r="F3" s="12">
+        <v>126.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="13">
-        <v>126.4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="22" t="s">
+      <c r="F4" s="12">
+        <v>124.9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="13">
-        <v>124.9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="22" t="s">
+      <c r="F5" s="12">
+        <v>123.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="13">
-        <v>123.4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="15">
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="14">
         <v>121.9</v>
       </c>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1409,10 +1420,10 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="F2" s="17">
+      <c r="A2" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="16">
         <v>120.4</v>
       </c>
     </row>

--- a/Tracking.xlsx
+++ b/Tracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c.campbell\source\LearningResourcesRepo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05CE6326-07A0-4FF7-AC00-98F4AA2ADB13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25292D07-4F85-4BC1-92DD-2932D324B9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -162,7 +162,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -181,6 +181,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -259,7 +267,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -318,6 +326,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1087,9 +1104,11 @@
       <c r="C5" s="1">
         <v>145.4</v>
       </c>
-      <c r="D5" s="1"/>
+      <c r="D5" s="5">
+        <v>144</v>
+      </c>
       <c r="E5" s="1"/>
-      <c r="F5" s="12">
+      <c r="F5" s="21">
         <v>144.1</v>
       </c>
       <c r="G5" s="1"/>
@@ -1106,7 +1125,7 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="12">
+      <c r="F6" s="21">
         <v>142.9</v>
       </c>
       <c r="G6" s="1"/>
@@ -1120,7 +1139,7 @@
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
-      <c r="F7" s="14">
+      <c r="F7" s="22">
         <v>141.4</v>
       </c>
       <c r="G7" s="4"/>
@@ -1128,6 +1147,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1179,7 +1199,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="15">
+      <c r="F2" s="23">
         <v>139.9</v>
       </c>
       <c r="G2" s="1"/>
@@ -1193,7 +1213,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="12">
+      <c r="F3" s="21">
         <v>138.4</v>
       </c>
       <c r="G3" s="1"/>
@@ -1207,7 +1227,7 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="12">
+      <c r="F4" s="21">
         <v>136.9</v>
       </c>
       <c r="G4" s="1"/>
@@ -1221,7 +1241,7 @@
       <c r="C5" s="18"/>
       <c r="D5" s="18"/>
       <c r="E5" s="18"/>
-      <c r="F5" s="14">
+      <c r="F5" s="22">
         <v>135.4</v>
       </c>
       <c r="G5" s="18"/>
@@ -1267,7 +1287,7 @@
       <c r="A2" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="12">
+      <c r="F2" s="21">
         <v>133.9</v>
       </c>
     </row>
@@ -1275,7 +1295,7 @@
       <c r="A3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="21">
         <v>132.4</v>
       </c>
     </row>
@@ -1283,7 +1303,7 @@
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="23">
         <v>130.9</v>
       </c>
     </row>
@@ -1295,7 +1315,7 @@
       <c r="C5" s="18"/>
       <c r="D5" s="18"/>
       <c r="E5" s="18"/>
-      <c r="F5" s="14">
+      <c r="F5" s="22">
         <v>129.4</v>
       </c>
       <c r="G5" s="18"/>
@@ -1341,7 +1361,7 @@
       <c r="A2" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="12">
+      <c r="F2" s="21">
         <v>127.9</v>
       </c>
     </row>
@@ -1349,7 +1369,7 @@
       <c r="A3" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="21">
         <v>126.4</v>
       </c>
     </row>
@@ -1357,7 +1377,7 @@
       <c r="A4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="21">
         <v>124.9</v>
       </c>
     </row>
@@ -1365,7 +1385,7 @@
       <c r="A5" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="21">
         <v>123.4</v>
       </c>
     </row>
@@ -1377,7 +1397,7 @@
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
       <c r="E6" s="18"/>
-      <c r="F6" s="14">
+      <c r="F6" s="22">
         <v>121.9</v>
       </c>
       <c r="G6" s="18"/>

--- a/Tracking.xlsx
+++ b/Tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c.campbell\source\LearningResourcesRepo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25292D07-4F85-4BC1-92DD-2932D324B9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10A3AF6-69EE-4A4B-AA73-1E5EDE48C03B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="39">
   <si>
     <t>Week Start</t>
   </si>
@@ -153,6 +153,12 @@
   </si>
   <si>
     <t>**Dehydration weight lol</t>
+  </si>
+  <si>
+    <t>1st april</t>
+  </si>
+  <si>
+    <t>7th april</t>
   </si>
 </sst>
 </file>
@@ -194,7 +200,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -222,6 +228,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -267,7 +279,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -327,14 +339,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1107,11 +1142,13 @@
       <c r="D5" s="5">
         <v>144</v>
       </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="21">
+      <c r="E5" s="1">
+        <v>143.80000000000001</v>
+      </c>
+      <c r="F5" s="21"/>
+      <c r="G5" s="28">
         <v>144.1</v>
       </c>
-      <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
         <v>36</v>
@@ -1125,10 +1162,10 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="21">
+      <c r="F6" s="21"/>
+      <c r="G6" s="28">
         <v>142.9</v>
       </c>
-      <c r="G6" s="1"/>
       <c r="H6" s="1"/>
     </row>
     <row r="7" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1136,14 +1173,12 @@
         <v>20</v>
       </c>
       <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="22">
-        <v>141.4</v>
-      </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1153,7 +1188,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D74EBFC-9222-4BC1-BD99-1A369ED9D387}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.44140625" customWidth="1"/>
@@ -1162,6 +1197,7 @@
     <col min="4" max="4" width="24.6640625" customWidth="1"/>
     <col min="5" max="5" width="28" customWidth="1"/>
     <col min="6" max="6" width="29" customWidth="1"/>
+    <col min="7" max="7" width="30.33203125" customWidth="1"/>
     <col min="8" max="8" width="29.77734375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1192,63 +1228,75 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="23">
-        <v>139.9</v>
-      </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
+      <c r="A2" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="24"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="29">
+        <v>141.4</v>
+      </c>
+      <c r="H2" s="22"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>22</v>
+      <c r="A3" s="13" t="s">
+        <v>38</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="21">
-        <v>138.4</v>
-      </c>
-      <c r="G3" s="1"/>
+      <c r="G3" s="30">
+        <v>139.9</v>
+      </c>
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="21">
+      <c r="G4" s="28">
+        <v>138.4</v>
+      </c>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="G5" s="28">
         <v>136.9</v>
       </c>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-    </row>
-    <row r="5" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="17" t="s">
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="22">
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="31">
         <v>135.4</v>
       </c>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
+      <c r="H6" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1256,6 +1304,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F756905-7F71-46E7-A371-7B3817CD3583}">
   <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="7" max="7" width="22.88671875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
@@ -1287,7 +1338,7 @@
       <c r="A2" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="21">
+      <c r="G2" s="28">
         <v>133.9</v>
       </c>
     </row>
@@ -1295,7 +1346,7 @@
       <c r="A3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="21">
+      <c r="G3" s="28">
         <v>132.4</v>
       </c>
     </row>
@@ -1303,7 +1354,7 @@
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="23">
+      <c r="G4" s="30">
         <v>130.9</v>
       </c>
     </row>
@@ -1315,10 +1366,10 @@
       <c r="C5" s="18"/>
       <c r="D5" s="18"/>
       <c r="E5" s="18"/>
-      <c r="F5" s="22">
+      <c r="F5" s="18"/>
+      <c r="G5" s="31">
         <v>129.4</v>
       </c>
-      <c r="G5" s="18"/>
       <c r="H5" s="18"/>
     </row>
   </sheetData>
@@ -1330,6 +1381,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEEB2055-4920-46DD-81EA-82AFF7E2861B}">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="7" max="7" width="15.44140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
@@ -1361,7 +1415,7 @@
       <c r="A2" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="21">
+      <c r="G2" s="28">
         <v>127.9</v>
       </c>
     </row>
@@ -1369,7 +1423,7 @@
       <c r="A3" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="21">
+      <c r="G3" s="28">
         <v>126.4</v>
       </c>
     </row>
@@ -1377,7 +1431,7 @@
       <c r="A4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="21">
+      <c r="G4" s="28">
         <v>124.9</v>
       </c>
     </row>
@@ -1385,7 +1439,7 @@
       <c r="A5" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="21">
+      <c r="G5" s="28">
         <v>123.4</v>
       </c>
     </row>
@@ -1397,10 +1451,10 @@
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
       <c r="E6" s="18"/>
-      <c r="F6" s="22">
+      <c r="F6" s="18"/>
+      <c r="G6" s="31">
         <v>121.9</v>
       </c>
-      <c r="G6" s="18"/>
       <c r="H6" s="18"/>
     </row>
   </sheetData>
@@ -1443,7 +1497,7 @@
       <c r="A2" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="F2" s="16">
+      <c r="F2" s="32">
         <v>120.4</v>
       </c>
     </row>

--- a/Tracking.xlsx
+++ b/Tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c.campbell\source\LearningResourcesRepo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10A3AF6-69EE-4A4B-AA73-1E5EDE48C03B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AFB84DE-EC91-4ABD-8ABA-D0405B49EE8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -279,7 +279,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -339,14 +339,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -359,7 +358,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -827,10 +826,9 @@
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
-      <c r="F9" s="12">
+      <c r="G9" s="12">
         <v>144.1</v>
       </c>
-      <c r="G9" s="1"/>
       <c r="H9" s="1"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -841,10 +839,9 @@
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
-      <c r="F10" s="12">
+      <c r="G10" s="12">
         <v>142.9</v>
       </c>
-      <c r="G10" s="1"/>
       <c r="H10" s="1"/>
     </row>
     <row r="11" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -855,10 +852,10 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
-      <c r="F11" s="14">
+      <c r="F11" s="18"/>
+      <c r="G11" s="14">
         <v>141.4</v>
       </c>
-      <c r="G11" s="4"/>
       <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -869,10 +866,9 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
-      <c r="F12" s="15">
+      <c r="G12" s="15">
         <v>139.9</v>
       </c>
-      <c r="G12" s="1"/>
       <c r="H12" s="1"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -883,10 +879,9 @@
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="12">
+      <c r="G13" s="12">
         <v>138.4</v>
       </c>
-      <c r="G13" s="1"/>
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -897,10 +892,9 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="12">
+      <c r="G14" s="12">
         <v>136.9</v>
       </c>
-      <c r="G14" s="1"/>
       <c r="H14" s="1"/>
     </row>
     <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -911,17 +905,17 @@
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
       <c r="E15" s="18"/>
-      <c r="F15" s="14">
+      <c r="F15" s="18"/>
+      <c r="G15" s="14">
         <v>135.4</v>
       </c>
-      <c r="G15" s="18"/>
       <c r="H15" s="18"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F16" s="12">
+      <c r="G16" s="12">
         <v>133.9</v>
       </c>
     </row>
@@ -929,7 +923,7 @@
       <c r="A17" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F17" s="12">
+      <c r="G17" s="12">
         <v>132.4</v>
       </c>
     </row>
@@ -937,7 +931,7 @@
       <c r="A18" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F18" s="15">
+      <c r="G18" s="15">
         <v>130.9</v>
       </c>
     </row>
@@ -949,17 +943,17 @@
       <c r="C19" s="18"/>
       <c r="D19" s="18"/>
       <c r="E19" s="18"/>
-      <c r="F19" s="14">
+      <c r="F19" s="18"/>
+      <c r="G19" s="14">
         <v>129.4</v>
       </c>
-      <c r="G19" s="18"/>
       <c r="H19" s="18"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F20" s="12">
+      <c r="G20" s="12">
         <v>127.9</v>
       </c>
     </row>
@@ -967,7 +961,7 @@
       <c r="A21" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F21" s="12">
+      <c r="G21" s="12">
         <v>126.4</v>
       </c>
     </row>
@@ -975,7 +969,7 @@
       <c r="A22" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F22" s="12">
+      <c r="G22" s="12">
         <v>124.9</v>
       </c>
     </row>
@@ -983,7 +977,7 @@
       <c r="A23" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F23" s="12">
+      <c r="G23" s="12">
         <v>123.4</v>
       </c>
     </row>
@@ -995,17 +989,17 @@
       <c r="C24" s="18"/>
       <c r="D24" s="18"/>
       <c r="E24" s="18"/>
-      <c r="F24" s="14">
+      <c r="F24" s="18"/>
+      <c r="G24" s="14">
         <v>121.9</v>
       </c>
-      <c r="G24" s="18"/>
       <c r="H24" s="18"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="F25" s="16">
+      <c r="G25" s="16">
         <v>120.4</v>
       </c>
     </row>
@@ -1145,8 +1139,7 @@
       <c r="E5" s="1">
         <v>143.80000000000001</v>
       </c>
-      <c r="F5" s="21"/>
-      <c r="G5" s="28">
+      <c r="G5" s="27">
         <v>144.1</v>
       </c>
       <c r="H5" s="1"/>
@@ -1162,8 +1155,7 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="28">
+      <c r="G6" s="27">
         <v>142.9</v>
       </c>
       <c r="H6" s="1"/>
@@ -1173,12 +1165,12 @@
         <v>20</v>
       </c>
       <c r="B7" s="4"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="25"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1228,18 +1220,18 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="29">
+      <c r="B2" s="23"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="28">
         <v>141.4</v>
       </c>
-      <c r="H2" s="22"/>
+      <c r="H2" s="21"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
@@ -1249,7 +1241,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="G3" s="30">
+      <c r="G3" s="29">
         <v>139.9</v>
       </c>
       <c r="H3" s="1"/>
@@ -1262,7 +1254,7 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
-      <c r="G4" s="28">
+      <c r="G4" s="27">
         <v>138.4</v>
       </c>
       <c r="H4" s="1"/>
@@ -1275,7 +1267,7 @@
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
-      <c r="G5" s="28">
+      <c r="G5" s="27">
         <v>136.9</v>
       </c>
       <c r="H5" s="1"/>
@@ -1289,7 +1281,7 @@
       <c r="D6" s="18"/>
       <c r="E6" s="18"/>
       <c r="F6" s="18"/>
-      <c r="G6" s="31">
+      <c r="G6" s="30">
         <v>135.4</v>
       </c>
       <c r="H6" s="18"/>
@@ -1338,7 +1330,7 @@
       <c r="A2" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="28">
+      <c r="G2" s="27">
         <v>133.9</v>
       </c>
     </row>
@@ -1346,7 +1338,7 @@
       <c r="A3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="28">
+      <c r="G3" s="27">
         <v>132.4</v>
       </c>
     </row>
@@ -1354,7 +1346,7 @@
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="30">
+      <c r="G4" s="29">
         <v>130.9</v>
       </c>
     </row>
@@ -1367,7 +1359,7 @@
       <c r="D5" s="18"/>
       <c r="E5" s="18"/>
       <c r="F5" s="18"/>
-      <c r="G5" s="31">
+      <c r="G5" s="30">
         <v>129.4</v>
       </c>
       <c r="H5" s="18"/>
@@ -1415,7 +1407,7 @@
       <c r="A2" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="28">
+      <c r="G2" s="27">
         <v>127.9</v>
       </c>
     </row>
@@ -1423,7 +1415,7 @@
       <c r="A3" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="28">
+      <c r="G3" s="27">
         <v>126.4</v>
       </c>
     </row>
@@ -1431,7 +1423,7 @@
       <c r="A4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="28">
+      <c r="G4" s="27">
         <v>124.9</v>
       </c>
     </row>
@@ -1439,7 +1431,7 @@
       <c r="A5" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="27">
         <v>123.4</v>
       </c>
     </row>
@@ -1452,7 +1444,7 @@
       <c r="D6" s="18"/>
       <c r="E6" s="18"/>
       <c r="F6" s="18"/>
-      <c r="G6" s="31">
+      <c r="G6" s="30">
         <v>121.9</v>
       </c>
       <c r="H6" s="18"/>
@@ -1497,7 +1489,7 @@
       <c r="A2" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="F2" s="32">
+      <c r="F2" s="31">
         <v>120.4</v>
       </c>
     </row>

--- a/Tracking.xlsx
+++ b/Tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c.campbell\source\LearningResourcesRepo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AFB84DE-EC91-4ABD-8ABA-D0405B49EE8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89608F80-F12C-4C4D-A006-D3E0E8D05DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>

--- a/Tracking.xlsx
+++ b/Tracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c.campbell\source\LearningResourcesRepo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89608F80-F12C-4C4D-A006-D3E0E8D05DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A08D68D-7A82-415B-A705-F897C8AE790C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -279,7 +279,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -369,6 +369,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1139,6 +1142,9 @@
       <c r="E5" s="1">
         <v>143.80000000000001</v>
       </c>
+      <c r="F5" s="32">
+        <v>143.4</v>
+      </c>
       <c r="G5" s="27">
         <v>144.1</v>
       </c>

--- a/Tracking.xlsx
+++ b/Tracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c.campbell\source\LearningResourcesRepo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A08D68D-7A82-415B-A705-F897C8AE790C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F7EF39-B035-4B5A-9BE3-E4249E45DDD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="42">
   <si>
     <t>Week Start</t>
   </si>
@@ -159,6 +159,36 @@
   </si>
   <si>
     <t>7th april</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">143.0 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>144.1</t>
+    </r>
+  </si>
+  <si>
+    <t>dw 142.0</t>
+  </si>
+  <si>
+    <t>dw 142.4</t>
   </si>
 </sst>
 </file>
@@ -168,7 +198,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -195,6 +225,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -370,7 +408,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1142,13 +1180,15 @@
       <c r="E5" s="1">
         <v>143.80000000000001</v>
       </c>
-      <c r="F5" s="32">
+      <c r="F5" s="1">
         <v>143.4</v>
       </c>
-      <c r="G5" s="27">
-        <v>144.1</v>
-      </c>
-      <c r="H5" s="1"/>
+      <c r="G5" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="32" t="s">
+        <v>41</v>
+      </c>
       <c r="I5" t="s">
         <v>36</v>
       </c>
@@ -1157,8 +1197,12 @@
       <c r="A6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
+      <c r="B6" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="1">
+        <v>144.4</v>
+      </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="G6" s="27">

--- a/Tracking.xlsx
+++ b/Tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c.campbell\source\LearningResourcesRepo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F7EF39-B035-4B5A-9BE3-E4249E45DDD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA0CEA71-D4A5-4CBE-BEE9-759793D4CFB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -317,7 +317,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -409,6 +409,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -695,11 +698,11 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.77734375" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="3" width="19.6640625" customWidth="1"/>
     <col min="4" max="4" width="19.109375" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="14.77734375" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
     <col min="7" max="7" width="15.5546875" customWidth="1"/>
     <col min="8" max="8" width="22.6640625" customWidth="1"/>
   </cols>
@@ -1062,7 +1065,7 @@
     <col min="5" max="5" width="29.5546875" customWidth="1"/>
     <col min="6" max="6" width="29" customWidth="1"/>
     <col min="7" max="7" width="27.109375" customWidth="1"/>
-    <col min="8" max="8" width="34.21875" customWidth="1"/>
+    <col min="8" max="8" width="34.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1203,8 +1206,15 @@
       <c r="C6" s="1">
         <v>144.4</v>
       </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
+      <c r="D6" s="1">
+        <v>143.6</v>
+      </c>
+      <c r="E6" s="1">
+        <v>143.4</v>
+      </c>
+      <c r="F6" s="33">
+        <v>146</v>
+      </c>
       <c r="G6" s="27">
         <v>142.9</v>
       </c>
@@ -1234,13 +1244,13 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.44140625" customWidth="1"/>
-    <col min="2" max="2" width="21.77734375" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" customWidth="1"/>
     <col min="3" max="3" width="23.88671875" customWidth="1"/>
     <col min="4" max="4" width="24.6640625" customWidth="1"/>
     <col min="5" max="5" width="28" customWidth="1"/>
     <col min="6" max="6" width="29" customWidth="1"/>
     <col min="7" max="7" width="30.33203125" customWidth="1"/>
-    <col min="8" max="8" width="29.77734375" customWidth="1"/>
+    <col min="8" max="8" width="29.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">

--- a/Tracking.xlsx
+++ b/Tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c.campbell\source\LearningResourcesRepo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA0CEA71-D4A5-4CBE-BEE9-759793D4CFB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{514BE5C0-EE3A-4BB6-8F41-88ACAE105A84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="44">
   <si>
     <t>Week Start</t>
   </si>
@@ -189,6 +189,12 @@
   </si>
   <si>
     <t>dw 142.4</t>
+  </si>
+  <si>
+    <t>141.4**</t>
+  </si>
+  <si>
+    <t>** after a week off. Week of drinking takeways, not much food over weekend. This might be dehydration weight</t>
   </si>
 </sst>
 </file>
@@ -317,7 +323,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -383,9 +389,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -396,9 +399,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -411,7 +411,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1186,10 +1195,10 @@
       <c r="F5" s="1">
         <v>143.4</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="32" t="s">
+      <c r="H5" s="30" t="s">
         <v>41</v>
       </c>
       <c r="I5" t="s">
@@ -1200,7 +1209,7 @@
       <c r="A6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="30" t="s">
         <v>40</v>
       </c>
       <c r="C6" s="1">
@@ -1212,10 +1221,10 @@
       <c r="E6" s="1">
         <v>143.4</v>
       </c>
-      <c r="F6" s="33">
+      <c r="F6" s="12">
         <v>146</v>
       </c>
-      <c r="G6" s="27">
+      <c r="G6" s="26">
         <v>142.9</v>
       </c>
       <c r="H6" s="1"/>
@@ -1225,12 +1234,12 @@
         <v>20</v>
       </c>
       <c r="B7" s="4"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="24"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1240,7 +1249,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D74EBFC-9222-4BC1-BD99-1A369ED9D387}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.44140625" customWidth="1"/>
@@ -1283,12 +1292,12 @@
       <c r="A2" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="28">
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="32">
         <v>141.4</v>
       </c>
       <c r="H2" s="21"/>
@@ -1297,11 +1306,13 @@
       <c r="A3" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="34" t="s">
+        <v>42</v>
+      </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="G3" s="29">
+      <c r="G3" s="27">
         <v>139.9</v>
       </c>
       <c r="H3" s="1"/>
@@ -1314,7 +1325,7 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
-      <c r="G4" s="27">
+      <c r="G4" s="26">
         <v>138.4</v>
       </c>
       <c r="H4" s="1"/>
@@ -1327,7 +1338,7 @@
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
-      <c r="G5" s="27">
+      <c r="G5" s="26">
         <v>136.9</v>
       </c>
       <c r="H5" s="1"/>
@@ -1341,10 +1352,15 @@
       <c r="D6" s="18"/>
       <c r="E6" s="18"/>
       <c r="F6" s="18"/>
-      <c r="G6" s="30">
+      <c r="G6" s="28">
         <v>135.4</v>
       </c>
       <c r="H6" s="18"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H10" t="s">
+        <v>43</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1390,7 +1406,7 @@
       <c r="A2" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="27">
+      <c r="G2" s="26">
         <v>133.9</v>
       </c>
     </row>
@@ -1398,7 +1414,7 @@
       <c r="A3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="27">
+      <c r="G3" s="26">
         <v>132.4</v>
       </c>
     </row>
@@ -1406,7 +1422,7 @@
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="29">
+      <c r="G4" s="27">
         <v>130.9</v>
       </c>
     </row>
@@ -1419,7 +1435,7 @@
       <c r="D5" s="18"/>
       <c r="E5" s="18"/>
       <c r="F5" s="18"/>
-      <c r="G5" s="30">
+      <c r="G5" s="28">
         <v>129.4</v>
       </c>
       <c r="H5" s="18"/>
@@ -1467,7 +1483,7 @@
       <c r="A2" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="27">
+      <c r="G2" s="26">
         <v>127.9</v>
       </c>
     </row>
@@ -1475,7 +1491,7 @@
       <c r="A3" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="27">
+      <c r="G3" s="26">
         <v>126.4</v>
       </c>
     </row>
@@ -1483,7 +1499,7 @@
       <c r="A4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="27">
+      <c r="G4" s="26">
         <v>124.9</v>
       </c>
     </row>
@@ -1491,7 +1507,7 @@
       <c r="A5" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="27">
+      <c r="G5" s="26">
         <v>123.4</v>
       </c>
     </row>
@@ -1504,7 +1520,7 @@
       <c r="D6" s="18"/>
       <c r="E6" s="18"/>
       <c r="F6" s="18"/>
-      <c r="G6" s="30">
+      <c r="G6" s="28">
         <v>121.9</v>
       </c>
       <c r="H6" s="18"/>
@@ -1549,7 +1565,7 @@
       <c r="A2" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="F2" s="31">
+      <c r="F2" s="29">
         <v>120.4</v>
       </c>
     </row>

--- a/Tracking.xlsx
+++ b/Tracking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c.campbell\source\LearningResourcesRepo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{514BE5C0-EE3A-4BB6-8F41-88ACAE105A84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B558CF-4779-44D7-B5CC-60FC168F3F31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1428" yWindow="2004" windowWidth="18276" windowHeight="9612" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -323,7 +323,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -418,9 +418,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1307,7 +1304,7 @@
         <v>38</v>
       </c>
       <c r="B3" s="33"/>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D3" s="1"/>

--- a/Tracking.xlsx
+++ b/Tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c.campbell\source\LearningResourcesRepo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B558CF-4779-44D7-B5CC-60FC168F3F31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A372074-13AC-4C72-A6A3-D30F16E0D8E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1428" yWindow="2004" windowWidth="18276" windowHeight="9612" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31440" yWindow="3945" windowWidth="18975" windowHeight="8880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="46">
   <si>
     <t>Week Start</t>
   </si>
@@ -195,6 +195,12 @@
   </si>
   <si>
     <t>** after a week off. Week of drinking takeways, not much food over weekend. This might be dehydration weight</t>
+  </si>
+  <si>
+    <t>150.8***</t>
+  </si>
+  <si>
+    <t>***went on a weed and booze binge. No doubt residual junk food weight</t>
   </si>
 </sst>
 </file>
@@ -244,7 +250,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -278,6 +284,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -323,7 +335,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -419,6 +431,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1307,9 +1326,12 @@
       <c r="C3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="G3" s="27">
+      <c r="D3" s="1">
+        <v>142.6</v>
+      </c>
+      <c r="E3" s="34"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="36">
         <v>139.9</v>
       </c>
       <c r="H3" s="1"/>
@@ -1318,7 +1340,9 @@
       <c r="A4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -1353,6 +1377,11 @@
         <v>135.4</v>
       </c>
       <c r="H6" s="18"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="H10" t="s">

--- a/Tracking.xlsx
+++ b/Tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c.campbell\source\LearningResourcesRepo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A372074-13AC-4C72-A6A3-D30F16E0D8E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29130D5B-AEA2-40FC-92FA-91EAB7CA5EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31440" yWindow="3945" windowWidth="18975" windowHeight="8880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="49">
   <si>
     <t>Week Start</t>
   </si>
@@ -202,6 +202,51 @@
   <si>
     <t>***went on a weed and booze binge. No doubt residual junk food weight</t>
   </si>
+  <si>
+    <t>complete blowout</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>143</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 144.1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>148.4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 142.9</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -210,7 +255,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,6 +290,12 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -289,7 +340,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -335,7 +386,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -430,6 +481,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -884,19 +938,34 @@
       <c r="F8" s="11">
         <v>145.6</v>
       </c>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
+      <c r="G8" s="11">
+        <v>144.4</v>
+      </c>
+      <c r="H8" s="11">
+        <v>144.6</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="G9" s="12">
-        <v>144.1</v>
+      <c r="B9" s="1">
+        <v>145.4</v>
+      </c>
+      <c r="C9" s="1">
+        <v>144</v>
+      </c>
+      <c r="D9" s="1">
+        <v>143.80000000000001</v>
+      </c>
+      <c r="E9" s="1">
+        <v>143.80000000000001</v>
+      </c>
+      <c r="F9" s="34">
+        <v>143.4</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="H9" s="1"/>
     </row>
@@ -904,12 +973,21 @@
       <c r="A10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="G10" s="12">
-        <v>142.9</v>
+      <c r="B10" s="19"/>
+      <c r="C10" s="1">
+        <v>144.4</v>
+      </c>
+      <c r="D10" s="1">
+        <v>143.6</v>
+      </c>
+      <c r="E10" s="1">
+        <v>143.4</v>
+      </c>
+      <c r="F10" s="34">
+        <v>146</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="H10" s="1"/>
     </row>
@@ -917,8 +995,12 @@
       <c r="A11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
+      <c r="B11" s="4">
+        <v>147.4</v>
+      </c>
+      <c r="C11" s="4">
+        <v>148.4</v>
+      </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="18"/>
@@ -933,8 +1015,12 @@
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
+      <c r="D12" s="1">
+        <v>142.6</v>
+      </c>
+      <c r="E12" s="1">
+        <v>143</v>
+      </c>
       <c r="G12" s="15">
         <v>139.9</v>
       </c>
@@ -944,10 +1030,21 @@
       <c r="A13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
+      <c r="B13" s="1">
+        <v>150.80000000000001</v>
+      </c>
+      <c r="C13" s="1">
+        <v>147.19999999999999</v>
+      </c>
+      <c r="D13" s="1">
+        <v>144.80000000000001</v>
+      </c>
+      <c r="E13" s="1">
+        <v>145.19999999999999</v>
+      </c>
+      <c r="F13">
+        <v>144.6</v>
+      </c>
       <c r="G13" s="12">
         <v>138.4</v>
       </c>
@@ -1329,9 +1426,9 @@
       <c r="D3" s="1">
         <v>142.6</v>
       </c>
-      <c r="E3" s="34"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="36">
+      <c r="E3" s="35"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="37">
         <v>139.9</v>
       </c>
       <c r="H3" s="1"/>
@@ -1343,9 +1440,18 @@
       <c r="B4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
+      <c r="C4" s="1">
+        <v>147.19999999999999</v>
+      </c>
+      <c r="D4" s="1">
+        <v>144.80000000000001</v>
+      </c>
+      <c r="E4" s="1">
+        <v>145.19999999999999</v>
+      </c>
+      <c r="F4" s="34">
+        <v>144.6</v>
+      </c>
       <c r="G4" s="26">
         <v>138.4</v>
       </c>
@@ -1384,6 +1490,10 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="36"/>
+      <c r="B10" t="s">
+        <v>46</v>
+      </c>
       <c r="H10" t="s">
         <v>43</v>
       </c>

--- a/Tracking.xlsx
+++ b/Tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c.campbell\source\LearningResourcesRepo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29130D5B-AEA2-40FC-92FA-91EAB7CA5EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8CBD8D-8C38-4CE0-94C6-740EFCA32B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33465" yWindow="1605" windowWidth="21855" windowHeight="11595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="48">
   <si>
     <t>Week Start</t>
   </si>
@@ -206,46 +206,7 @@
     <t>complete blowout</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>143</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 144.1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>148.4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 142.9</t>
-    </r>
+    <t>holiday/binging</t>
   </si>
 </sst>
 </file>
@@ -255,7 +216,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -294,14 +255,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -341,6 +296,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +347,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -481,9 +442,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -493,6 +451,23 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -773,7 +748,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.5546875" style="1" customWidth="1"/>
@@ -786,7 +761,7 @@
     <col min="8" max="8" width="22.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -812,7 +787,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -828,7 +803,7 @@
       </c>
       <c r="H2" s="7"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -842,7 +817,7 @@
       </c>
       <c r="H3" s="7"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -856,7 +831,7 @@
       </c>
       <c r="H4" s="7"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -872,7 +847,7 @@
       </c>
       <c r="H5" s="7"/>
     </row>
-    <row r="6" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>12</v>
       </c>
@@ -892,7 +867,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -919,7 +894,7 @@
       </c>
       <c r="J7" s="20"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -945,7 +920,7 @@
         <v>144.6</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>18</v>
       </c>
@@ -961,15 +936,13 @@
       <c r="E9" s="1">
         <v>143.80000000000001</v>
       </c>
-      <c r="F9" s="34">
+      <c r="F9" s="1">
         <v>143.4</v>
       </c>
-      <c r="G9" s="12" t="s">
-        <v>47</v>
-      </c>
+      <c r="G9" s="12"/>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>19</v>
       </c>
@@ -980,18 +953,16 @@
       <c r="D10" s="1">
         <v>143.6</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="38">
         <v>143.4</v>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="38">
         <v>146</v>
       </c>
-      <c r="G10" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="H10" s="1"/>
-    </row>
-    <row r="11" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G10" s="39"/>
+      <c r="H10" s="38"/>
+    </row>
+    <row r="11" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>20</v>
       </c>
@@ -1001,56 +972,57 @@
       <c r="C11" s="4">
         <v>148.4</v>
       </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="14">
-        <v>141.4</v>
-      </c>
-      <c r="H11" s="4"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="40"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
       <c r="D12" s="1">
         <v>142.6</v>
       </c>
       <c r="E12" s="1">
         <v>143</v>
       </c>
-      <c r="G12" s="15">
-        <v>139.9</v>
-      </c>
-      <c r="H12" s="1"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="F12" s="43"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="38"/>
+      <c r="J12" s="43"/>
+      <c r="K12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="37">
         <v>150.80000000000001</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="37">
         <v>147.19999999999999</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13" s="37">
         <v>144.80000000000001</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="37">
         <v>145.19999999999999</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="37">
         <v>144.6</v>
       </c>
       <c r="G13" s="12">
-        <v>138.4</v>
+        <v>144.6</v>
       </c>
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>23</v>
       </c>
@@ -1059,11 +1031,11 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="G14" s="12">
-        <v>136.9</v>
+        <v>143.1</v>
       </c>
       <c r="H14" s="1"/>
     </row>
-    <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="17" t="s">
         <v>24</v>
       </c>
@@ -1073,16 +1045,16 @@
       <c r="E15" s="18"/>
       <c r="F15" s="18"/>
       <c r="G15" s="14">
-        <v>135.4</v>
+        <v>141.6</v>
       </c>
       <c r="H15" s="18"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
         <v>25</v>
       </c>
       <c r="G16" s="12">
-        <v>133.9</v>
+        <v>140.1</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
@@ -1090,7 +1062,7 @@
         <v>26</v>
       </c>
       <c r="G17" s="12">
-        <v>132.4</v>
+        <v>138.6</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
@@ -1098,7 +1070,7 @@
         <v>27</v>
       </c>
       <c r="G18" s="15">
-        <v>130.9</v>
+        <v>137.1</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1111,7 +1083,7 @@
       <c r="E19" s="18"/>
       <c r="F19" s="18"/>
       <c r="G19" s="14">
-        <v>129.4</v>
+        <v>135.6</v>
       </c>
       <c r="H19" s="18"/>
     </row>
@@ -1120,7 +1092,7 @@
         <v>29</v>
       </c>
       <c r="G20" s="12">
-        <v>127.9</v>
+        <v>134.1</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
@@ -1128,7 +1100,7 @@
         <v>30</v>
       </c>
       <c r="G21" s="12">
-        <v>126.4</v>
+        <v>132.6</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
@@ -1136,7 +1108,7 @@
         <v>31</v>
       </c>
       <c r="G22" s="12">
-        <v>124.9</v>
+        <v>131.1</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
@@ -1144,7 +1116,7 @@
         <v>32</v>
       </c>
       <c r="G23" s="12">
-        <v>123.4</v>
+        <v>129.6</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1157,7 +1129,7 @@
       <c r="E24" s="18"/>
       <c r="F24" s="18"/>
       <c r="G24" s="14">
-        <v>121.9</v>
+        <v>128.1</v>
       </c>
       <c r="H24" s="18"/>
     </row>
@@ -1165,9 +1137,7 @@
       <c r="A25" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="G25" s="16">
-        <v>120.4</v>
-      </c>
+      <c r="G25" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1426,9 +1396,9 @@
       <c r="D3" s="1">
         <v>142.6</v>
       </c>
-      <c r="E3" s="35"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="37">
+      <c r="E3" s="34"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="36">
         <v>139.9</v>
       </c>
       <c r="H3" s="1"/>
@@ -1449,7 +1419,7 @@
       <c r="E4" s="1">
         <v>145.19999999999999</v>
       </c>
-      <c r="F4" s="34">
+      <c r="F4" s="1">
         <v>144.6</v>
       </c>
       <c r="G4" s="26">
@@ -1490,7 +1460,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="36"/>
+      <c r="A10" s="35"/>
       <c r="B10" t="s">
         <v>46</v>
       </c>

--- a/Tracking.xlsx
+++ b/Tracking.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c.campbell\source\repos\Learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90AB1F41-8DC2-43E2-B562-F2031726C008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B04758D4-2A8D-408D-9F58-3134C23CCA25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33600" yWindow="1830" windowWidth="20865" windowHeight="12330" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="8" r:id="rId1"/>
-    <sheet name="Aug-September" sheetId="9" r:id="rId2"/>
+    <sheet name="September" sheetId="15" r:id="rId2"/>
     <sheet name="October" sheetId="10" r:id="rId3"/>
     <sheet name="November" sheetId="11" r:id="rId4"/>
     <sheet name="December" sheetId="12" r:id="rId5"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="29">
   <si>
     <t>Week Start</t>
   </si>
@@ -85,65 +85,9 @@
     <t>29th</t>
   </si>
   <si>
-    <t>28th</t>
-  </si>
-  <si>
-    <t>Weight 26th: 144</t>
-  </si>
-  <si>
-    <t>Start weight on 26th August: 144</t>
-  </si>
-  <si>
-    <t>Breakfast: none</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dinner: </t>
   </si>
   <si>
-    <r>
-      <t>Lunch: Potato 221, egg salad 211</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>T: 432</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Dinner: quorn fillet 152, veg saus 120, micro veg 55 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>T: 327</t>
-    </r>
-  </si>
-  <si>
     <t>Snack:</t>
   </si>
   <si>
@@ -177,65 +121,20 @@
     <t>24th</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Exercise: circuits class 100, 2.4 mile walk 100 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color theme="5" tint="-0.249977111117893"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>T:200</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Snack: yoghurt 90, blueberries 45, apple: 80 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color theme="9" tint="-0.249977111117893"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>T: 215</t>
-    </r>
-  </si>
-  <si>
-    <t>Total cals: 974</t>
-  </si>
-  <si>
-    <t>Net cals: 774</t>
-  </si>
-  <si>
-    <t>E.O.D. notes</t>
+    <t>23rd</t>
+  </si>
+  <si>
+    <t>29th September</t>
+  </si>
+  <si>
+    <t>29th september</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -266,48 +165,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="11"/>
-      <color theme="9" tint="-0.249977111117893"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="11"/>
-      <color theme="5" tint="-0.249977111117893"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF00B050"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF00B050"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -329,7 +186,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -367,17 +224,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -522,34 +368,6 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -559,7 +377,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -571,57 +389,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -918,297 +711,184 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8206FAD7-1BF4-48F9-81CE-86B68A210312}">
-  <dimension ref="A1:H32"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B9DABB1-84FC-4036-AA33-7D2855374669}">
+  <dimension ref="A2:H9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.21875" customWidth="1"/>
-    <col min="2" max="2" width="63.6640625" customWidth="1"/>
-    <col min="3" max="3" width="39.21875" customWidth="1"/>
-    <col min="4" max="4" width="25.6640625" customWidth="1"/>
-    <col min="5" max="5" width="23.44140625" customWidth="1"/>
+    <col min="1" max="1" width="28.77734375" customWidth="1"/>
+    <col min="2" max="2" width="22.5546875" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" customWidth="1"/>
+    <col min="5" max="5" width="19.5546875" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="17.88671875" customWidth="1"/>
+    <col min="8" max="8" width="21.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
+    <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="F3" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="G3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="H3" s="11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="7"/>
-    </row>
-    <row r="9" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="26"/>
-      <c r="B11" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="26"/>
-      <c r="B12" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="26"/>
-      <c r="B13" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="26"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="26"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="26"/>
-      <c r="B16" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="4"/>
-      <c r="B17" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="4"/>
-      <c r="B18" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="30"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="4"/>
-      <c r="B20" s="31"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="4"/>
-      <c r="B21" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="4"/>
-      <c r="B22" s="30"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B23" s="27"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B24" s="27"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B25" s="27"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-    </row>
-    <row r="27" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" s="5">
-        <v>143.5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" s="5">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" s="5">
-        <v>140.5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" s="5">
-        <v>140.5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>13</v>
-      </c>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="19"/>
+      <c r="B5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="19"/>
+      <c r="B6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="19"/>
+      <c r="B7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="19"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="13"/>
+    </row>
+    <row r="9" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="20"/>
+      <c r="B9" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A4:A9"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1229,159 +909,161 @@
   <sheetData>
     <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="11" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="14"/>
-      <c r="B4" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>22</v>
+      <c r="A4" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="16"/>
-      <c r="B5" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="17" t="s">
-        <v>23</v>
+      <c r="A5" s="19"/>
+      <c r="B5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="16"/>
-      <c r="B6" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="17" t="s">
-        <v>18</v>
+      <c r="A6" s="19"/>
+      <c r="B6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="16"/>
-      <c r="B7" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" s="17" t="s">
-        <v>21</v>
+      <c r="A7" s="19"/>
+      <c r="B7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="16"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="17"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="13"/>
     </row>
     <row r="9" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="18"/>
-      <c r="B9" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" s="20" t="s">
-        <v>24</v>
+      <c r="A9" s="20"/>
+      <c r="B9" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1415,56 +1097,43 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="22"/>
+        <v>27</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="E23" s="16"/>
       <c r="F23" s="6">
         <v>139</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
+        <v>19</v>
+      </c>
       <c r="F24" s="6">
         <v>137.5</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
+        <v>20</v>
+      </c>
       <c r="F25" s="6">
         <v>136</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
+        <v>21</v>
+      </c>
       <c r="F26" s="6">
         <v>134.5</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
+        <v>22</v>
+      </c>
       <c r="F27" s="6">
         <v>133</v>
       </c>
@@ -1523,13 +1192,13 @@
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
-      <c r="F4" s="23">
+      <c r="F4" s="17">
         <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F5" s="5">
         <v>131.5</v>
@@ -1537,7 +1206,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F6" s="5">
         <v>130</v>
@@ -1553,7 +1222,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F8" s="5">
         <v>127</v>
@@ -1630,7 +1299,7 @@
       <c r="F7" s="6"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1646,159 +1315,159 @@
   <sheetData>
     <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="11" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="14"/>
-      <c r="B4" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>22</v>
+      <c r="A4" s="18"/>
+      <c r="B4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="16"/>
-      <c r="B5" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="17" t="s">
-        <v>23</v>
+      <c r="A5" s="19"/>
+      <c r="B5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="16"/>
-      <c r="B6" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="17" t="s">
-        <v>18</v>
+      <c r="A6" s="19"/>
+      <c r="B6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="16"/>
-      <c r="B7" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" s="17" t="s">
-        <v>21</v>
+      <c r="A7" s="19"/>
+      <c r="B7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="16"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="17"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="13"/>
     </row>
     <row r="9" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="18"/>
-      <c r="B9" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" s="20" t="s">
-        <v>24</v>
+      <c r="A9" s="20"/>
+      <c r="B9" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/Tracking.xlsx
+++ b/Tracking.xlsx
@@ -8,17 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c.campbell\source\repos\Learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B04758D4-2A8D-408D-9F58-3134C23CCA25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C43442-818F-47FD-8D37-E72CA63B7ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="8" r:id="rId1"/>
-    <sheet name="September" sheetId="15" r:id="rId2"/>
-    <sheet name="October" sheetId="10" r:id="rId3"/>
-    <sheet name="November" sheetId="11" r:id="rId4"/>
-    <sheet name="December" sheetId="12" r:id="rId5"/>
-    <sheet name="Template" sheetId="13" r:id="rId6"/>
+    <sheet name="October" sheetId="10" r:id="rId2"/>
+    <sheet name="November" sheetId="11" r:id="rId3"/>
+    <sheet name="December" sheetId="12" r:id="rId4"/>
+    <sheet name="Template" sheetId="13" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="39">
   <si>
     <t>Week Start</t>
   </si>
@@ -121,20 +120,188 @@
     <t>24th</t>
   </si>
   <si>
-    <t>23rd</t>
-  </si>
-  <si>
     <t>29th September</t>
   </si>
   <si>
     <t>29th september</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Monday 9am weight: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>154.2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Breakfast:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> N/A</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Lunch:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 2 egg salad, potato</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Dinner:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> quorn fillet, 2 veg sausages, microwave veg</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Snack:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 150g greek yoghurt, 45g blueberries</t>
+    </r>
+  </si>
+  <si>
+    <t>Morning weight:</t>
+  </si>
+  <si>
+    <r>
+      <t>Morning weight 9am:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 154.2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Exercise: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2.4 mile gym walk and circuits class</t>
+    </r>
+  </si>
+  <si>
+    <t>Daily thoughts</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>12:45 :</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Wasn't hungry enough for breakfast this morning. Hardly a massive surprise given last night's stoned munchies. Was 151lb yesterday afternoon lol. Not dreading the circuits class but expecting it to be tough after about 4 weeks of doing nothing</t>
+    </r>
+  </si>
+  <si>
+    <t>Pretty shocked at how much damage has been done over four weeks of my "birthday month" lol. I was at 141 last time I was weighing. Very much hoping that it's a lot of water retention. Started period last night as well, so maybe that's playing a part...Yeah right lol.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -165,6 +332,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -186,7 +362,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -373,11 +549,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -414,6 +618,50 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -711,194 +959,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B9DABB1-84FC-4036-AA33-7D2855374669}">
-  <dimension ref="A2:H9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="28.77734375" customWidth="1"/>
-    <col min="2" max="2" width="22.5546875" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="16.44140625" customWidth="1"/>
-    <col min="5" max="5" width="19.5546875" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="17.88671875" customWidth="1"/>
-    <col min="8" max="8" width="21.5546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="19"/>
-      <c r="B5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="19"/>
-      <c r="B6" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="19"/>
-      <c r="B7" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="19"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="13"/>
-    </row>
-    <row r="9" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="20"/>
-      <c r="B9" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A4:A9"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D4E9984-0BBF-4457-9FD4-3B0BA626E22D}">
-  <dimension ref="A2:K27"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.44140625" customWidth="1"/>
-    <col min="2" max="4" width="24.44140625" customWidth="1"/>
+    <col min="2" max="2" width="42.109375" style="21" customWidth="1"/>
+    <col min="3" max="4" width="24.44140625" customWidth="1"/>
     <col min="5" max="5" width="23.33203125" customWidth="1"/>
     <col min="6" max="6" width="21.5546875" customWidth="1"/>
     <col min="7" max="7" width="26.6640625" customWidth="1"/>
@@ -907,248 +974,299 @@
     <col min="10" max="10" width="23.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="9" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B7" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C7" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D7" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E7" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F7" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G7" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H7" s="31" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="7" t="s">
+    <row r="8" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="38" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="29"/>
+      <c r="B9" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="D9" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E9" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="F9" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="G9" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="H9" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="19"/>
-      <c r="B5" s="8" t="s">
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="29"/>
+      <c r="B10" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="D10" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="E10" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="F10" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="G10" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="H10" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="19"/>
-      <c r="B6" s="8" t="s">
+    </row>
+    <row r="11" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="29"/>
+      <c r="B11" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="D11" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="E11" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="F11" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="G11" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="H11" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="19"/>
-      <c r="B7" s="8" t="s">
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="29"/>
+      <c r="B12" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="D12" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="E12" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="F12" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="G12" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="H12" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="19"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="13"/>
-    </row>
-    <row r="9" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="20"/>
-      <c r="B9" s="14" t="s">
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="29"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+    </row>
+    <row r="14" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="29"/>
+      <c r="B14" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="D14" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="E14" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="F14" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="G14" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="H14" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="H9" s="15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="1" t="s">
+    </row>
+    <row r="15" spans="1:8" ht="87" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="33"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="33"/>
+    </row>
+    <row r="27" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B27" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C27" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D27" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E27" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F27" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="G27" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H22" s="2" t="s">
+      <c r="H27" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="6">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="25"/>
+      <c r="C28" s="3"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="6"/>
+      <c r="G28">
+        <v>152.69999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F24" s="6">
-        <v>137.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
+      <c r="F29" s="6"/>
+      <c r="G29">
+        <v>151.19999999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F25" s="6">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="4" t="s">
+      <c r="F30" s="6"/>
+      <c r="G30">
+        <v>149.69999999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F26" s="6">
-        <v>134.5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
+      <c r="F31" s="6"/>
+      <c r="G31">
+        <v>148.19999999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F27" s="6">
-        <v>133</v>
-      </c>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A8:A14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{158E0B27-54BA-4FAB-9255-64A9E0C8C3D7}">
   <dimension ref="A3:H8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1234,7 +1352,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3336DB0B-A10D-4BA6-A098-B36AA33003C0}">
   <dimension ref="A3:H8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1308,7 +1426,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B8794AE-3C09-443A-AFC4-6DC8AB060CA1}">
   <dimension ref="A2:H9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/Tracking.xlsx
+++ b/Tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c.campbell\source\repos\Learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C43442-818F-47FD-8D37-E72CA63B7ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81D45044-B657-4F64-968A-495CF69F0E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="49">
   <si>
     <t>Week Start</t>
   </si>
@@ -161,75 +161,6 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> N/A</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Lunch:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 2 egg salad, potato</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Dinner:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> quorn fillet, 2 veg sausages, microwave veg</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Snack:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 150g greek yoghurt, 45g blueberries</t>
     </r>
   </si>
   <si>
@@ -295,13 +226,216 @@
   </si>
   <si>
     <t>Pretty shocked at how much damage has been done over four weeks of my "birthday month" lol. I was at 141 last time I was weighing. Very much hoping that it's a lot of water retention. Started period last night as well, so maybe that's playing a part...Yeah right lol.</t>
+  </si>
+  <si>
+    <r>
+      <t>Morning weight:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>151.0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Exercise: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2.4 mile gym walk and spin class</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>08:42</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Glad to see a big drop from yesterday in weight. I'm a bit tender form circuits class yesterday but not as sore as I thought I'd be. Would be nice if I get under 150 by Saturday but we'll see how the body reacts. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Snack:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> N/A</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">total cals: </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Lunch:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 2 egg salad - 211, potato - 221</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Dinner:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> quorn fillet -160, 2 veg sausages - 120, microwave veg - 55. handful wedges ~ 200 </t>
+    </r>
+  </si>
+  <si>
+    <t>total cals: 967</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Breakfast: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>50g oats, yog and blueberries - 320</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Lunch: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2 egg salad - 211, potato - 176</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dinner: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">quorn fillet - 160, saus - 120, veg - 55 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Snack: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>banana 165g - 147</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">weed: 2 bowls of weed, no munchies </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -341,8 +475,32 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -361,6 +519,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="18">
     <border>
@@ -581,7 +745,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -610,15 +774,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -636,16 +791,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -658,10 +804,43 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -960,11 +1139,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D4E9984-0BBF-4457-9FD4-3B0BA626E22D}">
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.44140625" customWidth="1"/>
-    <col min="2" max="2" width="42.109375" style="21" customWidth="1"/>
+    <col min="2" max="2" width="48.5546875" style="18" customWidth="1"/>
     <col min="3" max="4" width="24.44140625" customWidth="1"/>
     <col min="5" max="5" width="23.33203125" customWidth="1"/>
     <col min="6" max="6" width="21.5546875" customWidth="1"/>
@@ -981,7 +1160,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
@@ -989,273 +1168,291 @@
       <c r="A7" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="C7" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="31" t="s">
+      <c r="D7" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="31" t="s">
+      <c r="E7" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="31" t="s">
+      <c r="F7" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="31" t="s">
+      <c r="G7" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="31" t="s">
+      <c r="H7" s="39" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="H8" s="38" t="s">
-        <v>33</v>
+      <c r="B8" s="42" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8" s="31" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="29"/>
-      <c r="B9" s="22" t="s">
+      <c r="A9" s="33"/>
+      <c r="B9" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="E9" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="26" t="s">
+      <c r="F9" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="26" t="s">
+      <c r="G9" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="26" t="s">
+      <c r="H9" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="26" t="s">
-        <v>16</v>
-      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="29"/>
-      <c r="B10" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="27" t="s">
+      <c r="A10" s="33"/>
+      <c r="B10" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="27" t="s">
+      <c r="E10" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="F10" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="27" t="s">
+      <c r="G10" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="G10" s="27" t="s">
+      <c r="H10" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="27" t="s">
-        <v>17</v>
-      </c>
     </row>
     <row r="11" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="29"/>
-      <c r="B11" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="27" t="s">
+      <c r="A11" s="33"/>
+      <c r="B11" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="E11" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="27" t="s">
+      <c r="F11" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="27" t="s">
+      <c r="G11" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="27" t="s">
+      <c r="H11" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="27" t="s">
-        <v>14</v>
-      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="29"/>
-      <c r="B12" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="27" t="s">
+      <c r="A12" s="33"/>
+      <c r="B12" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="27" t="s">
+      <c r="E12" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="27" t="s">
+      <c r="F12" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="27" t="s">
+      <c r="G12" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="27" t="s">
+      <c r="H12" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="27" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="29"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="8"/>
+      <c r="A13" s="33"/>
+      <c r="B13" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>40</v>
+      </c>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
     </row>
-    <row r="14" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="29"/>
-      <c r="B14" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="27" t="s">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="33"/>
+      <c r="B14" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="27" t="s">
+      <c r="E14" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="E14" s="27" t="s">
+      <c r="F14" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="27" t="s">
+      <c r="G14" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="G14" s="27" t="s">
+      <c r="H14" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="H14" s="27" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="87" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="33"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="33"/>
-    </row>
-    <row r="27" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="1" t="s">
+    </row>
+    <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="25"/>
+      <c r="B15" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="44"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="44"/>
+    </row>
+    <row r="16" spans="1:8" ht="115.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="27"/>
+    </row>
+    <row r="28" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B27" s="24" t="s">
+      <c r="B28" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C28" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D28" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F28" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="G28" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H27" s="2" t="s">
+      <c r="H28" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" s="25"/>
-      <c r="C28" s="3"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="6"/>
-      <c r="G28">
-        <v>152.69999999999999</v>
-      </c>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="B29" s="22"/>
+      <c r="C29" s="3"/>
+      <c r="E29" s="16"/>
       <c r="F29" s="6"/>
-      <c r="G29">
-        <v>151.19999999999999</v>
+      <c r="G29" s="37">
+        <v>152.69999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F30" s="6"/>
-      <c r="G30">
-        <v>149.69999999999999</v>
+      <c r="G30" s="37">
+        <v>151.19999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F31" s="6"/>
-      <c r="G31">
-        <v>148.19999999999999</v>
+      <c r="G31" s="37">
+        <v>149.69999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F32" s="6"/>
+      <c r="G32" s="37">
+        <v>148.19999999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F32" s="6"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1459,7 +1656,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="18"/>
+      <c r="A4" s="34"/>
       <c r="B4" s="7" t="s">
         <v>16</v>
       </c>
@@ -1483,7 +1680,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="19"/>
+      <c r="A5" s="35"/>
       <c r="B5" s="8" t="s">
         <v>17</v>
       </c>
@@ -1507,7 +1704,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="19"/>
+      <c r="A6" s="35"/>
       <c r="B6" s="8" t="s">
         <v>14</v>
       </c>
@@ -1531,7 +1728,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="19"/>
+      <c r="A7" s="35"/>
       <c r="B7" s="8" t="s">
         <v>15</v>
       </c>
@@ -1555,7 +1752,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="19"/>
+      <c r="A8" s="35"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
@@ -1565,7 +1762,7 @@
       <c r="H8" s="13"/>
     </row>
     <row r="9" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="20"/>
+      <c r="A9" s="36"/>
       <c r="B9" s="14" t="s">
         <v>18</v>
       </c>

--- a/Tracking.xlsx
+++ b/Tracking.xlsx
@@ -308,28 +308,17 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Snack: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">banana 165g - 147</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve">Snack:  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">greek yoghurt, blueberries – 135</t>
     </r>
   </si>
   <si>
@@ -339,7 +328,7 @@
     <t xml:space="preserve">total cals: 967</t>
   </si>
   <si>
-    <t xml:space="preserve">total cals: </t>
+    <t xml:space="preserve">total cals: 1178</t>
   </si>
   <si>
     <r>
@@ -405,6 +394,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">12:45 :</t>
     </r>
@@ -414,6 +404,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> Wasn't hungry enough for breakfast this morning. Hardly a massive surprise given last night's stoned munchies. Was 151lb yesterday afternoon lol. Not dreading the circuits class but expecting it to be tough after about 4 weeks of doing nothing
 </t>
@@ -426,6 +417,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">19:27:</t>
     </r>
@@ -436,6 +428,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -445,6 +438,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Feeling really good and loose after the circuits class. Was a lot less shit than I thought it would be </t>
     </r>
@@ -469,7 +463,29 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: Glad to see a big drop from yesterday in weight. I'm a bit tender form circuits class yesterday but not as sore as I thought I'd be. Would be nice if I get under 150 by Saturday but we'll see how the body reacts. </t>
+      <t xml:space="preserve">: Glad to see a big drop from yesterday in weight. I'm a bit tender form circuits class yesterday but not as sore as I thought I'd be. Would be nice if I get under 150 by Saturday but we'll see how the body reacts. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20:18</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> :  tough enough spin class but I still have the same stamina so that’s good. Pretty tired now, think it’s just hit me now that I’ve been home for about an hour</t>
     </r>
   </si>
   <si>
@@ -523,7 +539,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="hh:mm"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -593,27 +609,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <i val="true"/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -796,8 +791,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -869,7 +868,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -917,7 +916,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1041,12 +1040,12 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12.22"/>
   </cols>
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1067,312 +1066,313 @@
   <dimension ref="A1:K33"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="48.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="24.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="23.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="21.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="26.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="33.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="23.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="48.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="43.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="23.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="21.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="26.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="33.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="23.11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5"/>
-      <c r="B9" s="9" t="s">
+      <c r="A9" s="6"/>
+      <c r="B9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5"/>
-      <c r="B10" s="10" t="s">
+      <c r="A10" s="6"/>
+      <c r="B10" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="12" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5"/>
-      <c r="B11" s="10" t="s">
+      <c r="A11" s="6"/>
+      <c r="B11" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5"/>
-      <c r="B12" s="10" t="s">
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6"/>
+      <c r="B12" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="12" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5"/>
-      <c r="B13" s="12" t="s">
+      <c r="A13" s="6"/>
+      <c r="B13" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5"/>
-      <c r="B14" s="10" t="s">
+      <c r="A14" s="6"/>
+      <c r="B14" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="H14" s="11" t="s">
+      <c r="H14" s="12" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14"/>
-      <c r="B15" s="15" t="s">
+      <c r="A15" s="15"/>
+      <c r="B15" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="16"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="17"/>
     </row>
     <row r="16" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="22"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="22" t="s">
+      <c r="A28" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B28" s="23" t="s">
+      <c r="B28" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="C28" s="24" t="s">
+      <c r="C28" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="D28" s="24" t="s">
+      <c r="D28" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="E28" s="24" t="s">
+      <c r="E28" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="F28" s="24" t="s">
+      <c r="F28" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="G28" s="24" t="s">
+      <c r="G28" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="H28" s="24" t="s">
+      <c r="H28" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="I28" s="24"/>
-      <c r="J28" s="24"/>
-      <c r="K28" s="24"/>
+      <c r="I28" s="25"/>
+      <c r="J28" s="25"/>
+      <c r="K28" s="25"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="25" t="s">
+      <c r="A29" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="26"/>
-      <c r="C29" s="27"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="30" t="n">
+      <c r="B29" s="27"/>
+      <c r="C29" s="28"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="31" t="n">
         <v>152.7</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="25" t="s">
+      <c r="A30" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="F30" s="29"/>
-      <c r="G30" s="30" t="n">
+      <c r="F30" s="30"/>
+      <c r="G30" s="31" t="n">
         <v>151.2</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="25" t="s">
+      <c r="A31" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="F31" s="29"/>
-      <c r="G31" s="30" t="n">
+      <c r="F31" s="30"/>
+      <c r="G31" s="31" t="n">
         <v>149.7</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="25" t="s">
+      <c r="A32" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="F32" s="29"/>
-      <c r="G32" s="30" t="n">
+      <c r="F32" s="30"/>
+      <c r="G32" s="31" t="n">
         <v>148.2</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="25" t="s">
+      <c r="A33" s="26" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1398,78 +1398,78 @@
   <dimension ref="A3:H8"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.11"/>
   </cols>
   <sheetData>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="24" t="s">
+      <c r="G3" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="24" t="s">
+      <c r="H3" s="25" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="31" t="n">
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="32" t="n">
         <v>133</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="F5" s="32" t="n">
+      <c r="F5" s="33" t="n">
         <v>131.5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="32" t="n">
+      <c r="F6" s="33" t="n">
         <v>130</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="F7" s="32" t="n">
+      <c r="F7" s="33" t="n">
         <v>128.5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="F8" s="32" t="n">
+      <c r="F8" s="33" t="n">
         <v>127</v>
       </c>
     </row>
@@ -1493,65 +1493,65 @@
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="24" t="s">
+      <c r="G3" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="24" t="s">
+      <c r="H3" s="25" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="29"/>
-      <c r="G4" s="32" t="n">
+      <c r="F4" s="30"/>
+      <c r="G4" s="33" t="n">
         <v>125.5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="F5" s="29"/>
-      <c r="G5" s="32" t="n">
+      <c r="F5" s="30"/>
+      <c r="G5" s="33" t="n">
         <v>123</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="29"/>
-      <c r="G6" s="32" t="n">
+      <c r="F6" s="30"/>
+      <c r="G6" s="33" t="n">
         <v>121.5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="26" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="26" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1576,158 +1576,158 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="C3" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="E3" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="33" t="s">
+      <c r="F3" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="33" t="s">
+      <c r="G3" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="34" t="s">
+      <c r="H3" s="35" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="35"/>
-      <c r="B4" s="36" t="s">
+      <c r="A4" s="36"/>
+      <c r="B4" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="36" t="s">
+      <c r="D4" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="36" t="s">
+      <c r="G4" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="37" t="s">
+      <c r="H4" s="38" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="35"/>
-      <c r="B5" s="13" t="s">
+      <c r="A5" s="36"/>
+      <c r="B5" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="38" t="s">
+      <c r="H5" s="39" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="35"/>
-      <c r="B6" s="13" t="s">
+      <c r="A6" s="36"/>
+      <c r="B6" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="H6" s="38" t="s">
+      <c r="H6" s="39" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="35"/>
-      <c r="B7" s="13" t="s">
+      <c r="A7" s="36"/>
+      <c r="B7" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="38" t="s">
+      <c r="H7" s="39" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="35"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="38"/>
+      <c r="A8" s="36"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="39"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="35"/>
-      <c r="B9" s="39" t="s">
+      <c r="A9" s="36"/>
+      <c r="B9" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="C9" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="39" t="s">
+      <c r="E9" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="39" t="s">
+      <c r="F9" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="39" t="s">
+      <c r="G9" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="40" t="s">
+      <c r="H9" s="41" t="s">
         <v>30</v>
       </c>
     </row>

--- a/Tracking.xlsx
+++ b/Tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c.campbell\source\repos\Learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6507AD2-1688-43F7-B2D8-C3D2EE717D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{336508C8-A690-4086-9290-4912C32D1D94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="864" yWindow="672" windowWidth="17280" windowHeight="11448" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -597,7 +597,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>2 egg salad - 211, potato - 176</t>
+      <t>2 egg salad - 211, potato - 184</t>
     </r>
   </si>
 </sst>
@@ -938,12 +938,6 @@
   </cellStyleXfs>
   <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1036,6 +1030,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1461,9 +1461,9 @@
   <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.44140625" customWidth="1"/>
-    <col min="2" max="2" width="48.5546875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
-    <col min="4" max="4" width="24.44140625" customWidth="1"/>
+    <col min="2" max="2" width="48.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="39.33203125" customWidth="1"/>
+    <col min="4" max="4" width="43.33203125" customWidth="1"/>
     <col min="5" max="5" width="23.33203125" customWidth="1"/>
     <col min="6" max="6" width="21.5546875" customWidth="1"/>
     <col min="7" max="7" width="26.6640625" customWidth="1"/>
@@ -1488,287 +1488,287 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="10" t="s">
+      <c r="A9" s="46"/>
+      <c r="B9" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="41" t="s">
+      <c r="D9" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="11" t="s">
+      <c r="A10" s="46"/>
+      <c r="B10" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" s="10" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="11" t="s">
+      <c r="A11" s="46"/>
+      <c r="B11" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="H11" s="10" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="11" t="s">
+      <c r="A12" s="46"/>
+      <c r="B12" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="G12" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="H12" s="10" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="2"/>
-      <c r="B13" s="13" t="s">
+      <c r="A13" s="46"/>
+      <c r="B13" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="11" t="s">
+      <c r="A14" s="46"/>
+      <c r="B14" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="G14" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="H14" s="10" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="15"/>
-      <c r="B15" s="16" t="s">
+      <c r="A15" s="13"/>
+      <c r="B15" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="43" t="s">
+      <c r="C15" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="17"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="15"/>
     </row>
     <row r="16" spans="1:8" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="20" t="s">
+      <c r="C16" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="42" t="s">
+      <c r="D16" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="22"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="20"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="23" t="s">
+      <c r="A28" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B28" s="24" t="s">
+      <c r="B28" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C28" s="25" t="s">
+      <c r="C28" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="D28" s="25" t="s">
+      <c r="D28" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="E28" s="25" t="s">
+      <c r="E28" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="F28" s="25" t="s">
+      <c r="F28" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="G28" s="25" t="s">
+      <c r="G28" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="H28" s="25" t="s">
+      <c r="H28" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="I28" s="25"/>
-      <c r="J28" s="25"/>
-      <c r="K28" s="25"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="26" t="s">
+      <c r="A29" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="27"/>
-      <c r="C29" s="28"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="31">
+      <c r="B29" s="25"/>
+      <c r="C29" s="26"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="29">
         <v>149.6</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="26" t="s">
+      <c r="A30" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="F30" s="30"/>
-      <c r="G30" s="31"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="29"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="26" t="s">
+      <c r="A31" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="F31" s="30"/>
-      <c r="G31" s="31"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="29"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="26" t="s">
+      <c r="A32" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="F32" s="30"/>
-      <c r="G32" s="31"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="29"/>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="26" t="s">
+      <c r="A33" s="24" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1792,72 +1792,72 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="D3" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="25" t="s">
+      <c r="E3" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="F3" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="25" t="s">
+      <c r="G3" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="25" t="s">
+      <c r="H3" s="23" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="32">
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="30">
         <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="33">
+      <c r="F5" s="31">
         <v>131.5</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="33">
+      <c r="F6" s="31">
         <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="33">
+      <c r="F7" s="31">
         <v>128.5</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="F8" s="33">
+      <c r="F8" s="31">
         <v>127</v>
       </c>
     </row>
@@ -1873,65 +1873,65 @@
   <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="D3" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="25" t="s">
+      <c r="E3" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="F3" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="25" t="s">
+      <c r="G3" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="25" t="s">
+      <c r="H3" s="23" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="30"/>
-      <c r="G4" s="33">
+      <c r="F4" s="28"/>
+      <c r="G4" s="31">
         <v>125.5</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="30"/>
-      <c r="G5" s="33">
+      <c r="F5" s="28"/>
+      <c r="G5" s="31">
         <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="30"/>
-      <c r="G6" s="33">
+      <c r="F6" s="28"/>
+      <c r="G6" s="31">
         <v>121.5</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="24" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="24" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1957,197 +1957,197 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="34" t="s">
+      <c r="D3" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="34" t="s">
+      <c r="E3" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="34" t="s">
+      <c r="F3" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="34" t="s">
+      <c r="G3" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="35" t="s">
+      <c r="H3" s="33" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4"/>
-      <c r="B4" s="45" t="s">
+      <c r="A4" s="2"/>
+      <c r="B4" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="45" t="s">
+      <c r="C4" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="45" t="s">
+      <c r="D4" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="45" t="s">
+      <c r="E4" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="45" t="s">
+      <c r="F4" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="45" t="s">
+      <c r="G4" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="47" t="s">
+      <c r="H4" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="I4" s="44"/>
+      <c r="I4" s="42"/>
     </row>
     <row r="5" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="1"/>
-      <c r="B5" s="36" t="s">
+      <c r="A5" s="47"/>
+      <c r="B5" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="C5" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="36" t="s">
+      <c r="D5" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="36" t="s">
+      <c r="E5" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="36" t="s">
+      <c r="F5" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="36" t="s">
+      <c r="G5" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="37" t="s">
+      <c r="H5" s="35" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="14" t="s">
+      <c r="A6" s="47"/>
+      <c r="B6" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="38" t="s">
+      <c r="H6" s="36" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="14" t="s">
+      <c r="A7" s="47"/>
+      <c r="B7" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="38" t="s">
+      <c r="H7" s="36" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="14" t="s">
+      <c r="A8" s="47"/>
+      <c r="B8" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H8" s="38" t="s">
+      <c r="H8" s="36" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="38"/>
+      <c r="A9" s="47"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="36"/>
     </row>
     <row r="10" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="1"/>
-      <c r="B10" s="39" t="s">
+      <c r="A10" s="47"/>
+      <c r="B10" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="39" t="s">
+      <c r="D10" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="39" t="s">
+      <c r="E10" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="39" t="s">
+      <c r="F10" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="39" t="s">
+      <c r="G10" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="H10" s="40" t="s">
+      <c r="H10" s="38" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="46"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Tracking.xlsx
+++ b/Tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c.campbell\source\repos\Learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{336508C8-A690-4086-9290-4912C32D1D94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0CAA5E4-BB91-4652-9ED0-CEA384CDF9C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="864" yWindow="672" windowWidth="17280" windowHeight="11448" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="24285" windowHeight="11295" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -19,8 +19,19 @@
     <sheet name="December" sheetId="4" r:id="rId4"/>
     <sheet name="Template" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -29,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="63">
   <si>
     <r>
       <rPr>
@@ -598,6 +609,62 @@
         <family val="2"/>
       </rPr>
       <t>2 egg salad - 211, potato - 184</t>
+    </r>
+  </si>
+  <si>
+    <t>4-6lbs a month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morning weight: N/A </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Breakfast:  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>50g oats, yog and blueberries - 320</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Lunch: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>2 egg salad - 211, potato - 184</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>16:34</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>: In the office, hence the no weight this morning. Leaving at 5 for the body conditioning class. Long day but busy so don't feel as tired. Definitely would prefer to be going home instead of walking down to the gym, but "I can't be bothered" is not a genuine excuse lol</t>
     </r>
   </si>
 </sst>
@@ -936,7 +1003,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1030,6 +1097,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1440,14 +1510,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.33203125" customWidth="1"/>
-    <col min="2" max="2" width="14.77734375" customWidth="1"/>
-    <col min="3" max="3" width="15.77734375" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="15.88671875" customWidth="1"/>
-    <col min="6" max="6" width="12.21875" customWidth="1"/>
+    <col min="1" max="1" width="22.28515625" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1458,36 +1528,36 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K33"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.44140625" customWidth="1"/>
-    <col min="2" max="2" width="48.5546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="39.33203125" customWidth="1"/>
-    <col min="4" max="4" width="43.33203125" customWidth="1"/>
-    <col min="5" max="5" width="23.33203125" customWidth="1"/>
-    <col min="6" max="6" width="21.5546875" customWidth="1"/>
-    <col min="7" max="7" width="26.6640625" customWidth="1"/>
-    <col min="8" max="8" width="33.88671875" customWidth="1"/>
-    <col min="9" max="9" width="15.6640625" customWidth="1"/>
-    <col min="10" max="10" width="23.109375" customWidth="1"/>
+    <col min="1" max="1" width="17.42578125" customWidth="1"/>
+    <col min="2" max="2" width="48.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="39.28515625" customWidth="1"/>
+    <col min="4" max="4" width="43.28515625" customWidth="1"/>
+    <col min="5" max="5" width="41.28515625" customWidth="1"/>
+    <col min="6" max="6" width="35" customWidth="1"/>
+    <col min="7" max="7" width="26.7109375" customWidth="1"/>
+    <col min="8" max="8" width="33.85546875" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" customWidth="1"/>
+    <col min="10" max="10" width="23.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
@@ -1513,8 +1583,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="46" t="s">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="47" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="5" t="s">
@@ -1527,7 +1597,7 @@
         <v>43</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>11</v>
@@ -1539,8 +1609,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="46"/>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="47"/>
       <c r="B9" s="8" t="s">
         <v>12</v>
       </c>
@@ -1551,7 +1621,7 @@
         <v>48</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>13</v>
@@ -1563,8 +1633,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="46"/>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="47"/>
       <c r="B10" s="9" t="s">
         <v>14</v>
       </c>
@@ -1575,7 +1645,7 @@
         <v>57</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>15</v>
@@ -1587,8 +1657,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="46"/>
+    <row r="11" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="47"/>
       <c r="B11" s="9" t="s">
         <v>16</v>
       </c>
@@ -1611,8 +1681,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="46"/>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="47"/>
       <c r="B12" s="9" t="s">
         <v>19</v>
       </c>
@@ -1635,8 +1705,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="46"/>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="47"/>
       <c r="B13" s="11" t="s">
         <v>21</v>
       </c>
@@ -1649,8 +1719,8 @@
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="46"/>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="47"/>
       <c r="B14" s="9" t="s">
         <v>22</v>
       </c>
@@ -1673,7 +1743,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="B15" s="14" t="s">
         <v>25</v>
@@ -1687,7 +1757,7 @@
       <c r="G15" s="10"/>
       <c r="H15" s="15"/>
     </row>
-    <row r="16" spans="1:8" ht="230.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="165" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
         <v>26</v>
       </c>
@@ -1700,12 +1770,14 @@
       <c r="D16" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="E16" s="19"/>
+      <c r="E16" s="40" t="s">
+        <v>62</v>
+      </c>
       <c r="F16" s="19"/>
       <c r="G16" s="19"/>
       <c r="H16" s="20"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="21" t="s">
         <v>1</v>
       </c>
@@ -1734,7 +1806,7 @@
       <c r="J28" s="23"/>
       <c r="K28" s="23"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="24" t="s">
         <v>29</v>
       </c>
@@ -1746,30 +1818,39 @@
         <v>149.6</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="24" t="s">
         <v>30</v>
       </c>
       <c r="F30" s="28"/>
-      <c r="G30" s="29"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G30" s="29">
+        <v>148.1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="24" t="s">
         <v>31</v>
       </c>
       <c r="F31" s="28"/>
-      <c r="G31" s="29"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G31" s="29">
+        <v>146.6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="24" t="s">
         <v>32</v>
       </c>
       <c r="F32" s="28"/>
-      <c r="G32" s="29"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="G32" s="29">
+        <v>145.1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="24" t="s">
         <v>33</v>
+      </c>
+      <c r="G33" s="29">
+        <v>143.6</v>
       </c>
     </row>
   </sheetData>
@@ -1783,15 +1864,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A3:H8"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A3:K8"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.77734375" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" customWidth="1"/>
-    <col min="7" max="7" width="16.109375" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>1</v>
       </c>
@@ -1816,8 +1897,11 @@
       <c r="H3" s="23" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K3" s="46" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
         <v>34</v>
       </c>
@@ -1826,39 +1910,39 @@
       <c r="D4" s="26"/>
       <c r="E4" s="26"/>
       <c r="F4" s="30">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+        <v>142.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="24" t="s">
         <v>35</v>
       </c>
       <c r="F5" s="31">
-        <v>131.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+        <v>140.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
         <v>36</v>
       </c>
       <c r="F6" s="31">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+        <v>139.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
         <v>37</v>
       </c>
       <c r="F7" s="31">
-        <v>128.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+        <v>137.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
         <v>38</v>
       </c>
       <c r="F8" s="31">
-        <v>127</v>
+        <v>136.1</v>
       </c>
     </row>
   </sheetData>
@@ -1870,9 +1954,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A3:H8"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>1</v>
       </c>
@@ -1898,7 +1982,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
         <v>34</v>
       </c>
@@ -1907,7 +1991,7 @@
         <v>125.5</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="24" t="s">
         <v>39</v>
       </c>
@@ -1916,7 +2000,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
         <v>40</v>
       </c>
@@ -1925,12 +2009,12 @@
         <v>121.5</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
         <v>42</v>
       </c>
@@ -1944,19 +2028,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A3:I11"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.88671875" customWidth="1"/>
-    <col min="2" max="2" width="30.5546875" customWidth="1"/>
-    <col min="3" max="3" width="36.77734375" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" customWidth="1"/>
+    <col min="2" max="2" width="30.5703125" customWidth="1"/>
+    <col min="3" max="3" width="36.7109375" customWidth="1"/>
     <col min="4" max="4" width="27" customWidth="1"/>
-    <col min="5" max="5" width="19.77734375" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
-    <col min="8" max="8" width="20.88671875" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="8" max="8" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1982,7 +2066,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="43" t="s">
         <v>11</v>
@@ -2007,8 +2091,8 @@
       </c>
       <c r="I4" s="42"/>
     </row>
-    <row r="5" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="47"/>
+    <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="48"/>
       <c r="B5" s="34" t="s">
         <v>13</v>
       </c>
@@ -2031,8 +2115,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="47"/>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="48"/>
       <c r="B6" s="12" t="s">
         <v>15</v>
       </c>
@@ -2055,8 +2139,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="47"/>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="48"/>
       <c r="B7" s="12" t="s">
         <v>18</v>
       </c>
@@ -2079,8 +2163,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="47"/>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="48"/>
       <c r="B8" s="12" t="s">
         <v>20</v>
       </c>
@@ -2103,8 +2187,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="47"/>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="48"/>
       <c r="B9" s="12"/>
       <c r="C9" s="12"/>
       <c r="D9" s="12"/>
@@ -2113,8 +2197,8 @@
       <c r="G9" s="12"/>
       <c r="H9" s="36"/>
     </row>
-    <row r="10" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="47"/>
+    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="48"/>
       <c r="B10" s="37" t="s">
         <v>24</v>
       </c>
@@ -2137,7 +2221,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>26</v>
       </c>

--- a/Tracking.xlsx
+++ b/Tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c.campbell\source\repos\Learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0CAA5E4-BB91-4652-9ED0-CEA384CDF9C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6078C479-9471-4641-8A38-FCF97B599367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="24285" windowHeight="11295" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="76">
   <si>
     <r>
       <rPr>
@@ -193,6 +193,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">Dinner: </t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -202,32 +205,6 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Dinner: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">quorn fillet - 160, saus - 120, veg - 55 </t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Dinner: </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
       <t>Snack:</t>
     </r>
     <r>
@@ -246,29 +223,6 @@
   </si>
   <si>
     <t>total cals: 967</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Exercise: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>2.4 mile gym walk and circuits class</t>
-    </r>
   </si>
   <si>
     <r>
@@ -537,15 +491,6 @@
     <t>Exercise: rest day</t>
   </si>
   <si>
-    <t>Exercise: circuits</t>
-  </si>
-  <si>
-    <t>Exercise: powerpump</t>
-  </si>
-  <si>
-    <t>Exercise: spin</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -633,6 +578,142 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>16:34</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>: In the office, hence the no weight this morning. Leaving at 5 for the body conditioning class. Long day but busy so don't feel as tired. Definitely would prefer to be going home instead of walking down to the gym, but "I can't be bothered" is not a genuine excuse lol</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Morning weight: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>148.6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Breakfast:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 50g oats, yog and blueberries - 320</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dinner: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">quorn fillet - 160, saus - 120, veg - 55 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Lunch:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2 egg salad - 211, potato - 184</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dinner:  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">quorn fillet - 160, saus - 120, veg - 55 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Snack: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>greek yoghurt, blueberries – 135. hard boiled egg -78.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>2 ice lollys (130)</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">Lunch: </t>
     </r>
     <r>
@@ -642,8 +723,11 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>2 egg salad - 211, potato - 184</t>
-    </r>
+      <t>2 egg salad - 211, potato - 209</t>
+    </r>
+  </si>
+  <si>
+    <t>Note: exercise calories are not included like in the app (I estime 100 cals per class and 100 cals for the walking. Prob an overestimate)</t>
   </si>
   <si>
     <r>
@@ -654,17 +738,122 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>16:34</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>: In the office, hence the no weight this morning. Leaving at 5 for the body conditioning class. Long day but busy so don't feel as tired. Definitely would prefer to be going home instead of walking down to the gym, but "I can't be bothered" is not a genuine excuse lol</t>
+      <t>total cals:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 1418</t>
+    </r>
+  </si>
+  <si>
+    <t>Future Claire notes (lol)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>09:20:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Interesting work out last night, it was all body weight. 1 minute on, 20 seconds off, 5 exercises per round, 4 rounds. Was pretty intense but really enjoyed it.
+Feeling pretty relaxed in my body after the working out this week. Seems the weight loss has settled down into a more typical rate. I suppose a "real" gain of 7lbs for 4 weeks holidays isn't awful lol
+Got a bit snacky yesterday, need to be careful with the weed. Those wee rowntrees ice lollys are fine as long as I stop at 2 lol. But the last of the weed is tonight so next week I think my challenge will be missing it the first few evenings of the week.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dinner:  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>tuna - 170, potato - 184 - salad - 55</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Snack:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> yoghurt, blueberries - 135, ice lolly - 53</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Exercise: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>2.4 mile gym walk and circuits class</t>
+    </r>
+  </si>
+  <si>
+    <t>Exercise: 2.4 mile walk and circuits</t>
+  </si>
+  <si>
+    <t>Exercise:  2.4 mile walk and spin</t>
+  </si>
+  <si>
+    <t>Exercise:   2.4 mile walk and powerpump</t>
+  </si>
+  <si>
+    <t>weeed 2.5 bowls. had an apple and banana and 1 slim slice of sour dough bread which I didn’t count</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Resist the urge to get weed.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> You're probably hungover now and wanting it. Have a clean Sunday, you're in the office tomorrow. Have some m &amp; s treats (calories counted for of course) and a move in the evening instead. Then go up and read for an hour</t>
     </r>
   </si>
 </sst>
@@ -672,7 +861,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -755,6 +944,22 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1003,7 +1208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1106,6 +1311,22 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1510,14 +1731,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.28515625" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" customWidth="1"/>
+    <col min="1" max="1" width="22.33203125" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="15.88671875" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1528,36 +1749,41 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K33"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" customWidth="1"/>
-    <col min="2" max="2" width="48.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="39.28515625" customWidth="1"/>
-    <col min="4" max="4" width="43.28515625" customWidth="1"/>
-    <col min="5" max="5" width="41.28515625" customWidth="1"/>
+    <col min="1" max="1" width="24.33203125" customWidth="1"/>
+    <col min="2" max="2" width="48.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="39.33203125" customWidth="1"/>
+    <col min="4" max="4" width="43.33203125" customWidth="1"/>
+    <col min="5" max="5" width="41.33203125" customWidth="1"/>
     <col min="6" max="6" width="35" customWidth="1"/>
-    <col min="7" max="7" width="26.7109375" customWidth="1"/>
-    <col min="8" max="8" width="33.85546875" customWidth="1"/>
-    <col min="9" max="9" width="15.7109375" customWidth="1"/>
-    <col min="10" max="10" width="23.140625" customWidth="1"/>
+    <col min="7" max="7" width="26.6640625" customWidth="1"/>
+    <col min="8" max="8" width="33.88671875" customWidth="1"/>
+    <col min="9" max="9" width="15.6640625" customWidth="1"/>
+    <col min="10" max="10" width="23.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
@@ -1583,7 +1809,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="47" t="s">
         <v>9</v>
       </c>
@@ -1591,16 +1817,16 @@
         <v>10</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>11</v>
@@ -1609,22 +1835,22 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="47"/>
       <c r="B9" s="8" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>13</v>
+        <v>55</v>
+      </c>
+      <c r="F9" s="39" t="s">
+        <v>58</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>13</v>
@@ -1633,22 +1859,22 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="47"/>
       <c r="B10" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="G10" s="10" t="s">
         <v>15</v>
@@ -1657,127 +1883,147 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="47"/>
       <c r="B11" s="9" t="s">
         <v>16</v>
       </c>
       <c r="C11" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="10" t="s">
-        <v>18</v>
-      </c>
       <c r="E11" s="10" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="47"/>
       <c r="B12" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>20</v>
+      <c r="E12" s="9" t="s">
+        <v>62</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="47"/>
       <c r="B13" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
+      <c r="E13" s="49" t="s">
+        <v>65</v>
+      </c>
       <c r="F13" s="12"/>
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="47"/>
       <c r="B14" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H14" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C15" s="41" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
+      <c r="E15" s="50" t="s">
+        <v>74</v>
+      </c>
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
       <c r="H15" s="15"/>
     </row>
-    <row r="16" spans="1:8" ht="165" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
+    <row r="16" spans="1:8" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="52" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>28</v>
-      </c>
       <c r="D16" s="40" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E16" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="F16" s="19"/>
+        <v>56</v>
+      </c>
+      <c r="F16" s="51" t="s">
+        <v>67</v>
+      </c>
       <c r="G16" s="19"/>
       <c r="H16" s="20"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="101.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B17" s="53"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="54" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="21" t="s">
         <v>1</v>
       </c>
@@ -1806,9 +2052,9 @@
       <c r="J28" s="23"/>
       <c r="K28" s="23"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="24" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B29" s="25"/>
       <c r="C29" s="26"/>
@@ -1818,36 +2064,36 @@
         <v>149.6</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="24" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F30" s="28"/>
       <c r="G30" s="29">
         <v>148.1</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F31" s="28"/>
       <c r="G31" s="29">
         <v>146.6</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="24" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F32" s="28"/>
       <c r="G32" s="29">
         <v>145.1</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="24" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G33" s="29">
         <v>143.6</v>
@@ -1865,14 +2111,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A3:K8"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" customWidth="1"/>
-    <col min="3" max="3" width="16.140625" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" customWidth="1"/>
+    <col min="7" max="7" width="16.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>1</v>
       </c>
@@ -1898,12 +2144,12 @@
         <v>8</v>
       </c>
       <c r="K3" s="46" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="24" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B4" s="26"/>
       <c r="C4" s="26"/>
@@ -1913,33 +2159,33 @@
         <v>142.1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="24" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F5" s="31">
         <v>140.6</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="24" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F6" s="31">
         <v>139.1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="24" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F7" s="31">
         <v>137.6</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F8" s="31">
         <v>136.1</v>
@@ -1954,9 +2200,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A3:H8"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>1</v>
       </c>
@@ -1982,41 +2228,41 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="24" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F4" s="28"/>
       <c r="G4" s="31">
         <v>125.5</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="24" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F5" s="28"/>
       <c r="G5" s="31">
         <v>123</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="24" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F6" s="28"/>
       <c r="G6" s="31">
         <v>121.5</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="24" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -2028,19 +2274,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A3:I11"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="34.85546875" customWidth="1"/>
-    <col min="2" max="2" width="30.5703125" customWidth="1"/>
-    <col min="3" max="3" width="36.7109375" customWidth="1"/>
+    <col min="1" max="1" width="34.88671875" customWidth="1"/>
+    <col min="2" max="2" width="30.5546875" customWidth="1"/>
+    <col min="3" max="3" width="36.6640625" customWidth="1"/>
     <col min="4" max="4" width="27" customWidth="1"/>
-    <col min="5" max="5" width="19.7109375" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" customWidth="1"/>
-    <col min="8" max="8" width="20.85546875" customWidth="1"/>
+    <col min="5" max="5" width="19.6640625" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="8" width="20.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -2066,7 +2312,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2"/>
       <c r="B4" s="43" t="s">
         <v>11</v>
@@ -2091,7 +2337,7 @@
       </c>
       <c r="I4" s="42"/>
     </row>
-    <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="48"/>
       <c r="B5" s="34" t="s">
         <v>13</v>
@@ -2115,7 +2361,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="48"/>
       <c r="B6" s="12" t="s">
         <v>15</v>
@@ -2139,55 +2385,55 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="48"/>
       <c r="B7" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H7" s="36" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="48"/>
       <c r="B8" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H8" s="36" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="48"/>
       <c r="B9" s="12"/>
       <c r="C9" s="12"/>
@@ -2197,33 +2443,33 @@
       <c r="G9" s="12"/>
       <c r="H9" s="36"/>
     </row>
-    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="48"/>
       <c r="B10" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" s="38" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="C10" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" s="38" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="16" t="s">
-        <v>26</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
